--- a/dcf/AMZN.xlsx
+++ b/dcf/AMZN.xlsx
@@ -904,7 +904,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1186,25 +1186,25 @@
         <v>11</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>187.3582988083911</v>
+        <v>164.814174747181</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>179.5394692651875</v>
+        <v>157.9719181450328</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>172.0923343086484</v>
+        <v>151.4544388404339</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>164.9974784474168</v>
+        <v>145.2447849900448</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>158.2365865146644</v>
+        <v>139.3269650399637</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>151.7923765812307</v>
+        <v>133.6858891923483</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>145.6485372412758</v>
+        <v>128.3073146863969</v>
       </c>
     </row>
     <row r="6">
@@ -1212,25 +1212,25 @@
         <v>12</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>200.9721628336125</v>
+        <v>176.6833516422416</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>192.5447288187977</v>
+        <v>169.3104863812074</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>184.5187840160131</v>
+        <v>162.2883747076527</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>176.873328791046</v>
+        <v>155.5986836514873</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>169.5885546761811</v>
+        <v>149.2241197321596</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>162.6457716980508</v>
+        <v>143.1483655557722</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>156.027340444318</v>
+        <v>137.3560205459316</v>
       </c>
     </row>
     <row r="7">
@@ -1238,25 +1238,25 @@
         <v>13</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>214.586026858834</v>
+        <v>188.5525285373022</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>205.5499883724079</v>
+        <v>180.6490546173821</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>196.9452337233778</v>
+        <v>173.1223105748714</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>188.7491791346752</v>
+        <v>165.9525823129299</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>180.9405228376978</v>
+        <v>159.1212744243555</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>173.4991668148708</v>
+        <v>152.6108419191961</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>166.4061436473601</v>
+        <v>146.4047264054662</v>
       </c>
     </row>
     <row r="8">
@@ -1264,103 +1264,103 @@
         <v>14</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>228.1998908840554</v>
+        <v>200.4217054323628</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>218.5552479260181</v>
+        <v>191.9876228535567</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>209.3716834307425</v>
+        <v>183.9562464420902</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>200.6250294783044</v>
+        <v>176.3064809743724</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>192.2924909992144</v>
+        <v>169.0184291165515</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>184.352561931691</v>
+        <v>162.07331828262</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>176.7849468504023</v>
+        <v>155.4534322650008</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="52" t="n">
         <v>15</v>
       </c>
-      <c r="B9" s="8" t="n">
-        <v>241.8137549092769</v>
+      <c r="B9" s="53" t="n">
+        <v>212.2908823274234</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>231.5605074796283</v>
+        <v>203.3261910897313</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>221.7981331381072</v>
+        <v>194.790182309309</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>212.5008798219336</v>
+        <v>186.660379635815</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>203.6444591607311</v>
+        <v>178.9155838087474</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>195.2059570485111</v>
+        <v>171.5357946460439</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>187.1637500534444</v>
+        <v>164.5021381245354</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="52" t="n">
         <v>16</v>
       </c>
-      <c r="B10" s="8" t="n">
-        <v>255.4276189344983</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>244.5657670332385</v>
+      <c r="B10" s="53" t="n">
+        <v>224.160059222484</v>
+      </c>
+      <c r="C10" s="53" t="n">
+        <v>214.6647593259059</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>234.2245828454719</v>
+        <v>205.6241181765277</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>224.3767301655628</v>
+        <v>197.0142782972575</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>214.9964273222478</v>
+        <v>188.8127385009433</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>206.0593521653312</v>
+        <v>180.9982710094678</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>197.5425532564865</v>
+        <v>173.5508439840701</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="52" t="n">
         <v>17</v>
       </c>
-      <c r="B11" s="8" t="n">
-        <v>269.0414829597198</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>257.5710265868487</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>246.6510325528366</v>
+      <c r="B11" s="53" t="n">
+        <v>236.0292361175446</v>
+      </c>
+      <c r="C11" s="53" t="n">
+        <v>226.0033275620806</v>
+      </c>
+      <c r="D11" s="53" t="n">
+        <v>216.4580540437465</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>236.2525805091919</v>
+        <v>207.3681769587001</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>226.3483954837645</v>
+        <v>198.7098931931392</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>216.9127472821513</v>
+        <v>190.4607473728918</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>207.9213564595287</v>
+        <v>182.5995498436047</v>
       </c>
     </row>
     <row r="13">
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.9225056477214251</v>
+        <v>0.9207474227218065</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24599,7 +24599,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24751,13 +24751,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>200.6250294783044</v>
+        <v>176.3064809743724</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>298.0061189664989</v>
+        <v>255.9661059242913</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>129.386147290945</v>
+        <v>116.3338013295474</v>
       </c>
     </row>
     <row r="59">
